--- a/hpi_scraper/Technographic/coresignal/coresignal_data.xlsx
+++ b/hpi_scraper/Technographic/coresignal/coresignal_data.xlsx
@@ -445,11 +445,11 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="57" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="70" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
@@ -500,27 +500,27 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications</t>
+          <t>Sea Limited</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>singtel.com</t>
+          <t>sea.com</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>hive; logstash; react native; telstra; whatsapp; ucaas; group policy; commvault; microservices; kentik; recorded future; sns; mysql; confluence; recognize; adobe; slurm; unix; smartsheet; veeam; dell poweredge; cisco vpn; ansible; prototype; broadcom; asana; workbooks; litmus; ovirt; azure active directory; ruby; aeris; idirect; sap fico; fortinet; amazon ec2; github; google cloud; azure data factory; zeplin; f5 load balancer; mux; juniper routers; junit; invision; cisco asa; microsoft power automate; sandbox; docker; iam; google wallet; nuget; mlflow; martech; twitter; responsys; cisco firepower; elasticsearch; amazon eks; illumio; ocelot; laravel; hbase; cloudera cdh; financialforce; red hat; sap business objects; rpa; css; apache airflow; java; perl; keycloak; oracle server; azure databricks; apache; thousandeyes; cyberark; html5; sap hana; oracle exadata; microsoft teams; g data; apache kafka; google chrome; apache nifi; azure monitor; pytorch; oracle database; jira; microsoft azure active; cisco voip; cortex; nim; seagate; bitbucket pipelines; spectrum business; liveperson; microsoft excel; figma; dalet; gradle; microsoft powerapps; accenture; ibm unica; avaya; operative; cuda; harness; java api; jboss; prince2; xunit; hashicorp terraform; microsoft office; cch tagetik; zscaler; ssh; nagios; javascript; dom; adobe creative suite; salesforce; aws managed services; frontline education; nginx; git; yellowfin; liquibase; linux shell; pega; ibm watson; kvm; kibana; syslog; sap business suite; rabbitmq; axway; apache tomcat; velocloud; driven data; gxs; huawei; cisco nexus; php; wireshark; jasmine; openvpn; virtualbox; blockchain; netcracker; graphql; sis; google kubernetes engine; cisco aci; canva; megaport; bamboo; iridium; mlops; dynatrace; nodejs; launchpad; microsoft 365; tibco; idc; google analytics; qlikview; solarwinds; sd wan; spring boot; django; mule esb; livestream; pci; python; quip; automapper; blackberry; apache camel; sybase; apache spark; openid connect; oracle; jinja2; elastic stack; sap master data; mulesoft; arcgis; uipath; ams; kerberos; chef; postman; fintech; jenkins; cisco telepresence; cordial; coupa; jira service management; grafana; cacti; bcp; forter; ca spectrum; nms; redux; sap ariba; mongoose; sql script; xpress; influential; dash; bugzilla; cisco wireless; stripe; dart; google cloud platform; samsung; ubuntu; databricks; redis; jest; fireeye; rancher; openstack; microsoft sql server; adobe xd; outsystems; netgain; power bi; centos; sap financial accounting; sonarqube; sailpoint identityiq; pmd; informatica; mapr; radware; vmware cloud; red hat openshift; api gateway; infoblox; confluent kafka; coupa procurement; windows server; fico; atlassian bamboo; tds; postgresql; mulesoft anypoint platform; scada; facebook; j2ee; salesforce crm; zabbix; react; workday; puppet; terraform; f5 dns; grpc; kubernetes; mongodb; adobe photoshop; harmonic; tensorflow; dialogflow; minio; saml; soapui; oauth; metricstream; foundation software; confluent; angular; bash; argocd; helm; qualtrics; centricity; hashicorp; oracle 11g; zendesk; arista switches; velocloud sd wan; adobe acrobat; nutanix; netapp; saviynt; ceph; android devices; kms; dell; microsoft project; qlik; propel; suse; fortinet vpn; ivalua; memcached; wechat; webpack; mapi; cisco routers; g suite; webrtc; oracle linux; trustwave; elastic; typescript; sungard avantgard; sap credit management; bitbucket; linkedin; riverbed; tableau server; cloudera; json; sap erp; jumio; delinea; oracle responsys; blackline; symantec vip; successfactors; vmware esxi; nosql; okta; zeacom; prometheus; citrix workspace; elk; datadog; microsoft; cisco firewalls; asm; mobaxterm; splunk; callmanager; linux; jasper; i2i; servicenow; sap cloud platform; lenovo; salesforce sales cloud; sap successfactors; new relic; amobee; atlassian; flask; oracle cloud infrastructure; stitch; jira agile; telco systems; microsoft intune; oracle marketing cloud; suse linux; openai; symantec; gps; vds; swimlane; namely; powerdns; windows 10; forescout; netskope; chrome; youtube; github actions; citrix xenapp; viptela; cognos; swagger; html; gitlab; vmware; sql; brocade; selenium webdriver; nvidia; f5; bitsight; vmware vsphere; lucidchart; apache flink; quartz scheduler; heatmap; selenium; owasp; google ads; seg; automated insights; asp; microsoft office 365; tiktok; sungard; microsoft visio; rds; camunda; vmware horizon; togaf; microsoft azure; cisco meraki; apple watch; teradata; nominum; tenable; microsoft word; user interviews; vidyo; sailpoint; helpdesk; adobe experience manager; tableau; emc vnx; akamai; smokeping; jquery; css3; testng; scala; threatconnect; trend micro; apache jmeter; cisco catalyst; onramp; ignite digital; ekahau; media asset management; autocad; eastnets; archicad; sketchup; alm; odata; icertis; datarobot; mcafee; splunk enterprise; amazon connect; genesys; cisco webex; asic; mariadb; snort; yara; apache storm; infosys; jamf; microsoft windows server; mixpanel; sap training; crowdstrike; mobileiron; google bigquery; flutter; jupyter; presidio; pytest; hibernate; oracle weblogic; core hr; centric digital; nis; core dna; bpmn; dell boomi; macos; microsoft windows os; sqlalchemy; microsoft powerpoint; oran; mrtg; sap security; citrix provisioning services; cloud campaign; apple iphone; citrix xendesktop; hugging face; citrix netscaler; vmware vcloud director; storsimple; juniper switches; aws backup; sap process orchestration; tradeshift; zycus; dnn; oracle soa suite; cisco ios; oracle soa; aws cloudformation; adtech; firebase; jetpack; android studio; kotlin; scrum development; blue prism; cortex xsoar; istio; linkedin recruiter; openlayers; clickhouse; spring framework; improve digital; alteryx; amazon redshift; trifacta; persona; couchbase; trello; microsoft entra; elog; hubspot; rfpio; alibaba cloud; apache ant; ibwave design; kontera; salesforce soql; citynet; adconion; dmarc; salesforce cpq; autorabit; ibwave; oracle 12c; sybase database; sql advantage; software ag; webmethods; carbon black; docusign; sap concur; hootsuite; sqs; dds; hcm; blue coat; sysomos; sprinklr; huddle; cisco sourcefire; ccn; unify; whatsup gold; msi; recharge; mix; medium; segment; zoom; cucumber; eclipse; ecc; drift; square; quickbooks; unity; ups; charter; visa; spring; amp; juniper; stats; box; c; ease; instagram; reply; swift; thematic; market leader; sprint; network solutions; miro; deputy; impact; sentry; signal; hunter; upkeep; cashbook; debian; ecmascript; well; pwc; workable; google workspace; google dialogflow; aws lambda; appium; adobe premiere pro; mobilize; azure stack; cloudflare; microsoft active directory; google drive; bootstrap; msci; snowflake; cisco anyconnect; microsoft access; crisp; adobe analytics; google sites; ey; sustainalytics; onedrive; aws identity and; asp.net; control-m; scikit-learn; mac os; mockito; drupal; ibm mq; hp-ux; veritas; sophos; tenfold; inflight; widen; ruby on rails; hazelcast; winscp; q4; solidworks; sketch; oracle crm; sap business planning; ibm tivoli; podium; myob; appdynamics; zerto; ecm; hyperledger; ethereum; circleci; azure sentinel; encase; notion; open systems; aws security hub; imperva</t>
+          <t>mysql; nosql; jira; bash; ubuntu; oauth; chrome; microservices; redis; selenium; microsoft excel; figma; nvme; influential; react; google sheets; tableau; zoom rooms; macos; webpack; appsheet; grafana; appsflyer; centos; nms; scala; confluence; alteryx; sql; css; protobuf; bareos; palo alto firewalls; presto; dell san; boolean; linux; facebook ads; git; css3; inmobi; iam; junit; angular; google workspace; kubernetes; fortinet; helm; microsoft 365; youtube; hive; tiktok; clickup; redux; pci; nginx; selenium webdriver; vmware; flask; logstash; jira service desk; cisco anyconnect; cisco firewalls; splunk; nvidia; freshservice; google cloud; freshdesk; cisco nexus; mongodb; cisco switches; cuda; eslint; python; blockchain; linux shell; freepbx; fintech; hackerone; debian; google drive; cisco asa; jenkins; react native; helpdesk; graphql; servicenow; livestream; elastic; testrail; verizon; qlik; saltstack; f5; typescript; elk; power bi; django; docker; broadcom; windows server; idc; twitter; cisco routers; google ads; ansible; facebook; rpa; testng; openvpn; seagate; playwright; huawei switches; charles proxy; html5; pytorch; php; microsoft; pytest; centric digital; group policy; huawei; microsoft power bi; dell; javafx; gitlab; sd wan; crowdstrike; html; jupyter; trello; qlik sense; oracle 11g; appium; jest; google calendar; oracle; elasticsearch; sipp; java; kibana; hcm; twitch; centurylink; prometheus; grpc; user interviews; gmail; postman; greenhouse; github actions; zabbix; javascript; samsung; github; materialize; microsoft office; hugging face; openai; liveops; prototype; kotlin; arista switches; windows 10; whatsapp; workspace one; q4; tensorflow; latex; hbase; json; katalon; soapui; dql; postgresql; unix; honeywell; honeywell ebi; johnson controls metasys; autocad; kyriba; wireshark; ssh; tcpdump; red hat; linux kernel; salesforce; beyondtrust; jamf; cacti; flutter; veeam; looker; purecloud; google docs; openstack; rsa; rsa archer; vmware esxi; microsoft windows server; netsuite; acer; stats; ease; ups; amp; upkeep; box; tailwind; juniper; medium; segment; c; slack; market leader; charter; zoom; impact; instagram; storybook; network solutions; well; swift; apache hadoop; vmware vcenter; apache; intercom; ey; oracle ebs; haproxy; asana; openresty; nunit; vmware vsphere; terraform; nodejs; vue.js; ruby on rails; rabbitmq; cucumber; sprint; adobe; miro; transcend; visa; nagios; freshworks; zapier</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>cisco vpn; fortinet; juniper routers; cisco asa; cisco firepower; cisco voip; nagios; cisco nexus; cisco aci; cisco telepresence; cisco wireless; vmware cloud; windows server; arista switches; android devices; fortinet vpn; cisco routers; vmware esxi; cisco firewalls; microsoft intune; windows 10; vmware; vmware vsphere; vmware horizon; cisco meraki; cisco catalyst; cisco webex; jamf; microsoft windows server; mobileiron; macos; microsoft windows os; apple iphone; citrix xendesktop; vmware vcloud director; juniper switches; cisco ios; android studio; cisco sourcefire; sprint; cisco anyconnect</t>
+          <t>macos; palo alto firewalls; fortinet; vmware; cisco anyconnect; cisco firewalls; cisco nexus; cisco switches; cisco asa; windows server; cisco routers; huawei switches; arista switches; windows 10; jamf; vmware esxi; microsoft windows server; vmware vcenter; vmware vsphere; sprint; nagios</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>ucaas; microsoft teams; cisco voip; bitbucket pipelines; avaya; frontline education; php; launchpad; bitbucket; successfactors; sap successfactors; oracle cloud infrastructure; lucidchart; cisco webex; couchbase; zoom; cucumber; sprint; hp-ux</t>
+          <t>zoom rooms; freepbx; php; slack; zoom; cucumber; sprint</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>hive: last_seen=2026-06-01, first_seen=2025-08-17 | logstash: last_seen=2026-06-01, first_seen=2024-04-04 | react native: last_seen=2026-06-01, first_seen=2025-02-18 | telstra: last_seen=2026-06-01, first_seen=2025-08-17 | whatsapp: last_seen=2026-06-01, first_seen=2025-08-17 | ucaas: last_seen=2026-06-01, first_seen=2025-08-17 | group policy: last_seen=2026-06-01, first_seen=2025-08-17 | commvault: last_seen=2026-06-01, first_seen=2024-04-04 | microservices: last_seen=2026-06-01, first_seen=2025-08-17 | kentik: last_seen=2026-06-01, first_seen=2025-08-17 | recorded future: last_seen=2026-06-01, first_seen=2025-10-27 | sns: last_seen=2026-06-01, first_seen=2024-04-04 | mysql: last_seen=2026-06-01, first_seen=2024-04-04 | confluence: last_seen=2026-06-01, first_seen=2025-08-17 | recognize: last_seen=2026-06-01, first_seen=2024-04-04 | adobe: last_seen=2026-06-01, first_seen=2024-04-04 | slurm: last_seen=2026-06-01, first_seen=2025-09-07 | unix: last_seen=2026-06-01, first_seen=2024-04-04 | smartsheet: last_seen=2026-06-01, first_seen=2026-04-06 | veeam: last_seen=2026-06-01, first_seen=2024-04-04 | dell poweredge: last_seen=2026-06-01, first_seen=2025-10-26 | cisco vpn: last_seen=2026-06-01, first_seen=2026-06-01 | ansible: last_seen=2026-06-01, first_seen=2024-04-04 | prototype: last_seen=2026-06-01, first_seen=2024-04-04 | broadcom: last_seen=2026-06-01, first_seen=2025-08-17 | asana: last_seen=2026-06-01, first_seen=2024-09-09 | workbooks: last_seen=2026-06-01, first_seen=2025-08-17 | litmus: last_seen=2026-06-01, first_seen=2025-10-07 | ovirt: last_seen=2026-06-01, first_seen=2025-10-05 | azure active directory: last_seen=2026-06-01, first_seen=2024-04-04 | ruby: last_seen=2026-06-01, first_seen=2025-08-17 | aeris: last_seen=2026-06-01, first_seen=2025-10-27 | idirect: last_seen=2026-06-01, first_seen=2025-08-17 | sap fico: last_seen=2026-06-01, first_seen=2024-04-04 | fortinet: last_seen=2026-06-01, first_seen=2024-04-04 | amazon ec2: last_seen=2026-06-01, first_seen=2024-05-20 | github: last_seen=2026-06-01, first_seen=2024-04-04 | google cloud: last_seen=2026-06-01, first_seen=2024-04-04 | azure data factory: last_seen=2026-06-01, first_seen=2024-07-15 | zeplin: last_seen=2026-06-01, first_seen=2025-08-17 | f5 load balancer: last_seen=2026-06-01, first_seen=2025-08-17 | mux: last_seen=2026-06-01, first_seen=2025-08-17 | juniper routers: last_seen=2026-06-01, first_seen=2025-08-17 | junit: last_seen=2026-06-01, first_seen=2024-04-04 | invision: last_seen=2026-06-01, first_seen=2024-04-04 | cisco asa: last_seen=2026-06-01, first_seen=2024-11-25 | microsoft power automate: last_seen=2026-06-01, first_seen=2025-02-18 | sandbox: last_seen=2026-06-01, first_seen=2025-08-17 | docker: last_seen=2026-06-01, first_seen=2024-04-04 | iam: last_seen=2026-06-01, first_seen=2024-04-04 | google wallet: last_seen=2026-06-01, first_seen=2025-08-24 | nuget: last_seen=2026-06-01, first_seen=2025-08-17 | mlflow: last_seen=2026-06-01, first_seen=2025-08-17 | martech: last_seen=2026-06-01, first_seen=2024-04-04 | twitter: last_seen=2026-06-01, first_seen=2024-06-10 | responsys: last_seen=2026-06-01, first_seen=2024-04-04 | cisco firepower: last_seen=2026-06-01, first_seen=2025-08-17 | elasticsearch: last_seen=2026-06-01, first_seen=2024-04-04 | amazon eks: last_seen=2026-06-01, first_seen=2024-12-06 | illumio: last_seen=2026-06-01, first_seen=2026-05-04 | ocelot: last_seen=2026-06-01, first_seen=2025-08-17 | laravel: last_seen=2026-06-01, first_seen=2024-05-20 | hbase: last_seen=2026-06-01, first_seen=2024-04-04 | cloudera cdh: last_seen=2026-06-01, first_seen=2026-01-25 | financialforce: last_seen=2026-06-01, first_seen=2026-01-19 | red hat: last_seen=2026-06-01, first_seen=2024-04-04 | sap business objects: last_seen=2026-06-01, first_seen=2026-04-06 | rpa: last_seen=2026-06-01, first_seen=2025-08-17 | css: last_seen=2026-06-01, first_seen=2025-08-17 | apache airflow: last_seen=2026-06-01, first_seen=2025-08-05 | java: last_seen=2026-06-01, first_seen=2024-04-04 | perl: last_seen=2026-06-01, first_seen=2025-08-17 | keycloak: last_seen=2026-06-01, first_seen=2026-04-28 | oracle server: last_seen=2026-06-01, first_seen=2026-01-26 | azure databricks: last_seen=2026-06-01, first_seen=2024-05-20 | apache: last_seen=2026-06-01, first_seen=2024-04-04 | thousandeyes: last_seen=2026-06-01, first_seen=2026-01-25 | cyberark: last_seen=2026-06-01, first_seen=2024-05-20 | html5: last_seen=2026-06-01, first_seen=2025-08-17 | sap hana: last_seen=2026-06-01, first_seen=2024-04-04 | oracle exadata: last_seen=2026-06-01, first_seen=2025-08-17 | microsoft teams: last_seen=2026-06-01, first_seen=2025-02-18 | g data: last_seen=2026-06-01, first_seen=2025-08-17 | apache kafka: last_seen=2026-06-01, first_seen=2025-02-20 | google chrome: last_seen=2026-06-01, first_seen=2025-08-17 | apache nifi: last_seen=2026-06-01, first_seen=2025-12-22 | azure monitor: last_seen=2026-06-01, first_seen=2024-04-04 | pytorch: last_seen=2026-06-01, first_seen=2025-08-17 | oracle database: last_seen=2026-06-01, first_seen=2024-04-04 | jira: last_seen=2026-06-01, first_seen=2025-08-17 | microsoft azure active: last_seen=2026-06-01, first_seen=2025-02-20 | cisco voip: last_seen=2026-06-01, first_seen=2024-05-20 | cortex: last_seen=2026-06-01, first_seen=2025-08-17 | nim: last_seen=2026-06-01, first_seen=2025-08-17 | seagate: last_seen=2026-06-01, first_seen=2025-08-17 | bitbucket pipelines: last_seen=2026-06-01, first_seen=2024-04-04 | spectrum business: last_seen=2026-06-01, first_seen=2026-05-04 | liveperson: last_seen=2026-06-01, first_seen=2025-08-17 | microsoft excel: last_seen=2026-06-01, first_seen=2025-02-18 | figma: last_seen=2026-06-01, first_seen=2024-04-04 | dalet: last_seen=2026-06-01, first_seen=2024-05-20 | gradle: last_seen=2026-06-01, first_seen=2025-08-17 | microsoft powerapps: last_seen=2026-06-01, first_seen=2026-01-04 | accenture: last_seen=2026-06-01, first_seen=2025-08-17 | ibm unica: last_seen=2026-06-01, first_seen=2026-01-25 | avaya: last_seen=2026-06-01, first_seen=2024-04-04 | operative: last_seen=2026-06-01, first_seen=2024-05-20 | cuda: last_seen=2026-06-01, first_seen=2025-09-07 | harness: last_seen=2026-06-01, first_seen=2025-08-17 | java api: last_seen=2026-06-01, first_seen=2025-08-17 | jboss: last_seen=2026-06-01, first_seen=2024-04-04 | prince2: last_seen=2026-06-01, first_seen=2025-08-17 | xunit: last_seen=2026-06-01, first_seen=2025-08-17 | hashicorp terraform: last_seen=2026-06-01, first_seen=2025-08-17 | microsoft office: last_seen=2026-06-01, first_seen=2025-02-18 | cch tagetik: last_seen=2026-06-01, first_seen=2025-08-17 | zscaler: last_seen=2026-06-01, first_seen=2024-05-20 | ssh: last_seen=2026-06-01, first_seen=2026-01-26 | nagios: last_seen=2026-06-01, first_seen=2024-04-04 | javascript: last_seen=2026-06-01, first_seen=2024-04-04 | dom: last_seen=2026-06-01, first_seen=2025-08-17 | adobe creative suite: last_seen=2026-06-01, first_seen=2025-08-17 | salesforce: last_seen=2026-06-01, first_seen=2024-04-04 | aws managed services: last_seen=2026-06-01, first_seen=2025-08-17 | frontline education: last_seen=2026-06-01, first_seen=2025-07-07 | nginx: last_seen=2026-06-01, first_seen=2024-04-04 | git: last_seen=2026-06-01, first_seen=2024-04-04 | yellowfin: last_seen=2026-06-01, first_seen=2025-08-17 | liquibase: last_seen=2026-06-01, first_seen=2024-12-06 | linux shell: last_seen=2026-06-01, first_seen=2025-08-17 | pega: last_seen=2026-06-01, first_seen=2025-09-29 | ibm watson: last_seen=2026-06-01, first_seen=2025-08-17 | kvm: last_seen=2026-06-01, first_seen=2025-08-17 | kibana: last_seen=2026-06-01, first_seen=2025-08-17 | syslog: last_seen=2026-06-01, first_seen=2026-04-27 | sap business suite: last_seen=2026-06-01, first_seen=2026-04-27 | rabbitmq: last_seen=2026-06-01, first_seen=2024-04-04 | axway: last_seen=2026-06-01, first_seen=2025-08-17 | apache tomcat: last_seen=2026-06-01, first_seen=2025-02-18 | velocloud: last_seen=2026-06-01, first_seen=2025-08-17 | driven data: last_seen=2026-06-01, first_seen=2025-08-17 | gxs: last_seen=2026-06-01, first_seen=2025-08-17 | huawei: last_seen=2026-06-01, first_seen=2025-08-17 | cisco nexus: last_seen=2026-06-01, first_seen=2025-08-17 | php: last_seen=2026-06-01, first_seen=2024-04-04 | wireshark: last_seen=2026-06-01, first_seen=2024-04-04 | jasmine: last_seen=2026-06-01, first_seen=2026-01-26 | openvpn: last_seen=2026-06-01, first_seen=2024-04-22 | virtualbox: last_seen=2026-06-01, first_seen=2025-08-17 | blockchain: last_seen=2026-06-01, first_seen=2025-08-17 | netcracker: last_seen=2026-06-01, first_seen=2025-08-17 | graphql: last_seen=2026-06-01, first_seen=2024-04-04 | sis: last_seen=2026-06-01, first_seen=2025-08-17 | google kubernetes engine: last_seen=2026-06-01, first_seen=2026-05-18 | cisco aci: last_seen=2026-06-01, first_seen=2024-04-04 | canva: last_seen=2026-06-01, first_seen=2024-04-04 | megaport: last_seen=2026-06-01, first_seen=2025-08-17 | bamboo: last_seen=2026-06-01, first_seen=2024-04-04 | iridium: last_seen=2026-06-01, first_seen=2025-08-17 | mlops: last_seen=2026-06-01, first_seen=2025-08-17 | dynatrace: last_seen=2026-06-01, first_seen=2024-04-04 | nodejs: last_seen=2026-06-01, first_seen=2025-04-08 | launchpad: last_seen=2026-06-01, first_seen=2025-08-17 | microsoft 365: last_seen=2026-06-01, first_seen=2025-08-17 | tibco: last_seen=2026-06-01, first_seen=2024-05-06 | idc: last_seen=2026-06-01, first_seen=2025-08-17 | google analytics: last_seen=2026-06-01, first_seen=2024-04-04 | qlikview: last_seen=2026-06-01, first_seen=2024-05-20 | solarwinds: last_seen=2026-06-01, first_seen=2024-05-20 | sd wan: last_seen=2026-06-01, first_seen=2025-08-17 | spring boot: last_seen=2026-06-01, first_seen=2025-02-18 | django: last_seen=2026-06-01, first_seen=2024-04-04 | mule esb: last_seen=2026-06-01, first_seen=2025-08-05 | livestream: last_seen=2026-06-01, first_seen=2025-08-17 | pci: last_seen=2026-06-01, first_seen=2025-08-17 | python: last_seen=2026-06-01, first_seen=2024-04-04 | quip: last_seen=2026-06-01, first_seen=2024-05-20 | automapper: last_seen=2026-06-01, first_seen=2025-08-17 | blackberry: last_seen=2026-06-01, first_seen=2025-08-17 | apache camel: last_seen=2026-06-01, first_seen=2025-08-17 | sybase: last_seen=2026-06-01, first_seen=2025-08-17 | apache spark: last_seen=2026-06-01, first_seen=2025-02-18 | openid connect: last_seen=2026-06-01, first_seen=2025-08-17 | oracle: last_seen=2026-06-01, first_seen=2025-08-17 | jinja2: last_seen=2026-06-01, first_seen=2025-08-05 | elastic stack: last_seen=2026-06-01, first_seen=2026-01-26 | sap master data: last_seen=2026-06-01, first_seen=2025-08-31 | mulesoft: last_seen=2026-06-01, first_seen=2024-04-04 | arcgis: last_seen=2026-06-01, first_seen=2025-11-11 | uipath: last_seen=2026-06-01, first_seen=2024-04-04 | ams: last_seen=2026-06-01, first_seen=2025-08-17 | kerberos: last_seen=2026-06-01, first_seen=2025-08-17 | chef: last_seen=2026-06-01, first_seen=2024-04-04 | postman: last_seen=2026-06-01, first_seen=2024-04-04 | fintech: last_seen=2026-06-01, first_seen=2025-08-17 | jenkins: last_seen=2026-06-01, first_seen=2024-04-04 | cisco telepresence: last_seen=2026-06-01, first_seen=2026-01-25 | cordial: last_seen=2026-06-01, first_seen=2025-09-29 | coupa: last_seen=2026-06-01, first_seen=2025-08-17 | jira service management: last_seen=2026-06-01, first_seen=2025-10-26 | grafana: last_seen=2026-06-01, first_seen=2024-04-04 | cacti: last_seen=2026-06-01, first_seen=2025-08-17 | bcp: last_seen=2026-06-01, first_seen=2025-08-17 | forter: last_seen=2026-06-01, first_seen=2026-01-25 | ca spectrum: last_seen=2026-06-01, first_seen=2025-08-17 | nms: last_seen=2026-06-01, first_seen=2025-08-17 | redux: last_seen=2026-06-01, first_seen=2024-04-04 | sap ariba: last_seen=2026-06-01, first_seen=2024-04-04 | mongoose: last_seen=2026-06-01, first_seen=2025-08-17 | sql script: last_seen=2026-06-01, first_seen=2025-08-17 | xpress: last_seen=2026-06-01, first_seen=2025-08-17 | influential: last_seen=2026-06-01, first_seen=2024-04-04 | dash: last_seen=2026-06-01, first_seen=2025-08-17 | bugzilla: last_seen=2026-06-01, first_seen=2024-05-20 | cisco wireless: last_seen=2026-06-01, first_seen=2025-08-17 | stripe: last_seen=2026-06-01, first_seen=2024-05-20 | dart: last_seen=2026-06-01, first_seen=2026-03-01 | google cloud platform: last_seen=2026-06-01, first_seen=2025-02-18 | samsung: last_seen=2026-06-01, first_seen=2025-08-17 | ubuntu: last_seen=2026-06-01, first_seen=2024-04-22 | databricks: last_seen=2026-06-01, first_seen=2024-04-04 | redis: last_seen=2026-06-01, first_seen=2024-04-04 | jest: last_seen=2026-06-01, first_seen=2025-08-17 | fireeye: last_seen=2026-06-01, first_seen=2025-08-17 | rancher: last_seen=2026-06-01, first_seen=2025-08-17 | openstack: last_seen=2026-06-01, first_seen=2024-04-04 | microsoft sql server: last_seen=2026-06-01, first_seen=2025-08-05 | adobe xd: last_seen=2026-06-01, first_seen=2025-02-18 | outsystems: last_seen=2026-06-01, first_seen=2025-08-17 | netgain: last_seen=2026-06-01, first_seen=2026-02-02 | power bi: last_seen=2026-06-01, first_seen=2025-08-17 | centos: last_seen=2026-06-01, first_seen=2024-05-20 | sap financial accounting: last_seen=2026-06-01, first_seen=2026-04-06 | sonarqube: last_seen=2026-06-01, first_seen=2024-04-04 | sailpoint identityiq: last_seen=2026-06-01, first_seen=2026-04-27 | pmd: last_seen=2026-06-01, first_seen=2025-08-17 | informatica: last_seen=2026-06-01, first_seen=2024-05-20 | mapr: last_seen=2026-06-01, first_seen=2025-08-17 | radware: last_seen=2026-06-01, first_seen=2025-08-17 | vmware cloud: last_seen=2026-06-01, first_seen=2025-08-17 | red hat openshift: last_seen=2026-06-01, first_seen=2025-10-20 | api gateway: last_seen=2026-06-01, first_seen=2025-08-17 | infoblox: last_seen=2026-06-01, first_seen=2024-08-05 | confluent kafka: last_seen=2026-06-01, first_seen=2025-08-17 | coupa procurement: last_seen=2026-06-01, first_seen=2026-05-04 | windows server: last_seen=2026-06-01, first_seen=2025-08-17 | fico: last_seen=2026-06-01, first_seen=2025-12-01 | atlassian bamboo: last_seen=2026-06-01, first_seen=2026-04-28 | tds: last_seen=2026-06-01, first_seen=2026-01-04 | postgresql: last_seen=2026-06-01, first_seen=2024-04-04 | mulesoft anypoint platform: last_seen=2026-06-01, first_seen=2026-01-19 | scada: last_seen=2026-06-01, first_seen=2026-01-11 | facebook: last_seen=2026-06-01, first_seen=2024-05-20 | j2ee: last_seen=2026-06-01, first_seen=2024-04-04 | salesforce crm: last_seen=2026-06-01, first_seen=2025-02-20 | zabbix: last_seen=2026-06-01, first_seen=2024-04-04 | react: last_seen=2026-06-01, first_seen=2024-04-04 | workday: last_seen=2026-06-01, first_seen=2024-11-25 | puppet: last_seen=2026-06-01, first_seen=2024-04-04 | terraform: last_seen=2026-06-01, first_seen=2024-04-04 | f5 dns: last_seen=2026-06-01, first_seen=2025-08-17 | grpc: last_seen=2026-06-01, first_seen=2025-08-17 | kubernetes: last_seen=2026-06-01, first_seen=2024-04-04 | mongodb: last_seen=2026-06-01, first_seen=2024-04-04 | adobe photoshop: last_seen=2026-06-01, first_seen=2025-02-18 | harmonic: last_seen=2026-06-01, first_seen=2025-08-17 | tensorflow: last_seen=2026-06-01, first_seen=2025-08-17 | dialogflow: last_seen=2026-06-01, first_seen=2025-08-17 | minio: last_seen=2026-06-01, first_seen=2026-03-09 | saml: last_seen=2026-06-01, first_seen=2025-08-17 | soapui: last_seen=2026-06-01, first_seen=2024-04-04 | oauth: last_seen=2026-06-01, first_seen=2025-08-17 | metricstream: last_seen=2026-06-01, first_seen=2025-08-17 | foundation software: last_seen=2026-06-01, first_seen=2025-08-17 | confluent: last_seen=2026-06-01, first_seen=2025-08-17 | angular: last_seen=2026-06-01, first_seen=2024-04-04 | bash: last_seen=2026-06-01, first_seen=2025-08-17 | argocd: last_seen=2026-06-01, first_seen=2025-08-17 | helm: last_seen=2026-06-01, first_seen=2025-08-17 | qualtrics: last_seen=2026-06-01, first_seen=2024-04-22 | centricity: last_seen=2026-06-01, first_seen=2025-08-17 | hashicorp: last_seen=2026-06-01, first_seen=2024-04-04 | oracle 11g: last_seen=2026-06-01, first_seen=2026-01-26 | zendesk: last_seen=2026-06-01, first_seen=2025-10-26 | arista switches: last_seen=2026-06-01, first_seen=2025-08-17 | velocloud sd wan: last_seen=2026-06-01, first_seen=2025-08-17 | adobe acrobat: last_seen=2026-06-01, first_seen=2025-08-17 | nutanix: last_seen=2026-06-01, first_seen=2024-04-04 | netapp: last_seen=2026-06-01, first_seen=2024-04-04 | saviynt: last_seen=2026-06-01, first_seen=2026-05-04 | ceph: last_seen=2026-06-01, first_seen=2026-03-09 | android devices: last_seen=2026-06-01, first_seen=2025-08-17 | kms: last_seen=2026-06-01, first_seen=2025-08-05 | dell: last_seen=2026-06-01, first_seen=2024-04-04 | microsoft project: last_seen=2026-06-01, first_seen=2025-08-05 | qlik: last_seen=2026-06-01, first_seen=2025-01-13 | propel: last_seen=2026-06-01, first_seen=2025-08-17 | suse: last_seen=2026-06-01, first_seen=2025-08-17 | fortinet vpn: last_seen=2026-06-01, first_seen=2025-11-24 | ivalua: last_seen=2026-06-01, first_seen=2025-08-17 | memcached: last_seen=2026-06-01, first_seen=2024-05-20 | wechat: last_seen=2026-06-01, first_seen=2025-08-17 | webpack: last_seen=2026-06-01, first_seen=2024-04-04 | mapi: last_seen=2026-06-01, first_seen=2025-09-07 | cisco routers: last_seen=2026-06-01, first_seen=2024-04-04 | g suite: last_seen=2026-06-01, first_seen=2025-02-20 | webrtc: last_seen=2026-06-01, first_seen=2025-04-08 | oracle linux: last_seen=2026-06-01, first_seen=2024-04-04 | trustwave: last_seen=2026-06-01, first_seen=2024-05-20 | elastic: last_seen=2026-06-01, first_seen=2025-08-17 | typescript: last_seen=2026-06-01, first_seen=2025-08-17 | sungard avantgard: last_seen=2026-06-01, first_seen=2025-12-01 | sap credit management: last_seen=2026-06-01, first_seen=2026-02-16 | bitbucket: last_seen=2026-06-01, first_seen=2025-08-17 | linkedin: last_seen=2026-06-01, first_seen=2024-04-04 | riverbed: last_seen=2026-06-01, first_seen=2025-08-17 | tableau server: last_seen=2026-06-01, first_seen=2025-04-08 | cloudera: last_seen=2026-06-01, first_seen=2024-04-04 | json: last_seen=2026-06-01, first_seen=2024-04-04 | sap erp: last_seen=2026-06-01, first_seen=2025-08-17 | jumio: last_seen=2026-06-01, first_seen=2026-01-25 | delinea: last_seen=2026-06-01, first_seen=2025-10-05 | oracle responsys: last_seen=2026-06-01, first_seen=2025-08-17 | blackline: last_seen=2026-06-01, first_seen=2025-08-17 | symantec vip: last_seen=2026-06-01, first_seen=2026-02-15 | successfactors: last_seen=2026-06-01, first_seen=2024-04-04 | vmware esxi: last_seen=2026-06-01, first_seen=2025-03-03 | nosql: last_seen=2026-06-01, first_seen=2024-04-04 | okta: last_seen=2026-06-01, first_seen=2024-04-04 | zeacom: last_seen=2026-06-01, first_seen=2025-08-17 | prometheus: last_seen=2026-06-01, first_seen=2024-04-04 | citrix workspace: last_seen=2026-06-01, first_seen=2025-08-17 | elk: last_seen=2026-06-01, first_seen=2024-04-04 | datadog: last_seen=2026-06-01, first_seen=2024-04-04 | microsoft: last_seen=2026-06-01, first_seen=2024-04-04 | cisco firewalls: last_seen=2026-06-01, first_seen=2025-08-17 | asm: last_seen=2026-06-01, first_seen=2026-01-26 | mobaxterm: last_seen=2026-06-01, first_seen=2026-01-11 | splunk: last_seen=2026-06-01, first_seen=2024-04-04 | callmanager: last_seen=2026-06-01, first_seen=2025-04-08 | linux: last_seen=2026-06-01, first_seen=2024-04-04 | jasper: last_seen=2026-06-01, first_seen=2025-08-17 | i2i: last_seen=2026-06-01, first_seen=2025-08-17 | servicenow: last_seen=2026-06-01, first_seen=2024-04-04 | sap cloud platform: last_seen=2026-06-01, first_seen=2025-03-24 | lenovo: last_seen=2026-06-01, first_seen=2026-01-25 | salesforce sales cloud: last_seen=2026-06-01, first_seen=2025-08-17 | sap successfactors: last_seen=2026-06-01, first_seen=2025-08-17 | new relic: last_seen=2026-06-01, first_seen=2024-04-04 | amobee: last_seen=2026-06-01, first_seen=2025-08-17 | atlassian: last_seen=2026-06-01, first_seen=2025-08-17 | flask: last_seen=2026-06-01, first_seen=2025-08-17 | oracle cloud infrastructure: last_seen=2026-06-01, first_seen=2025-06-16 | stitch: last_seen=2026-06-01, first_seen=2025-08-17 | jira agile: last_seen=2026-06-01, first_seen=2026-04-28 | telco systems: last_seen=2026-06-01, first_seen=2025-08-17 | microsoft intune: last_seen=2026-06-01, first_seen=2025-02-18 | oracle marketing cloud: last_seen=2026-06-01, first_seen=2024-04-04 | suse linux: last_seen=2026-06-01, first_seen=2026-01-26 | openai: last_seen=2026-06-01, first_seen=2024-07-09 | symantec: last_seen=2026-06-01, first_seen=2024-05-20 | gps: last_seen=2026-06-01, first_seen=2025-08-17 | vds: last_seen=2026-06-01, first_seen=2025-08-17 | swimlane: last_seen=2026-06-01, first_seen=2025-08-24 | namely: last_seen=2026-06-01, first_seen=2024-04-04 | powerdns: last_seen=2026-06-01, first_seen=2025-08-17 | windows 10: last_seen=2026-06-01, first_seen=2024-04-04 | forescout: last_seen=2026-06-01, first_seen=2024-08-05 | netskope: last_seen=2026-06-01, first_seen=2024-07-29 | chrome: last_seen=2026-06-01, first_seen=2024-04-04 | youtube: last_seen=2026-06-01, first_seen=2024-05-20 | github actions: last_seen=2026-06-01, first_seen=2025-02-18 | citrix xenapp: last_seen=2026-06-01, first_seen=2024-04-04 | viptela: last_seen=2026-06-01, first_seen=2025-08-17 | cognos: last_seen=2026-06-01, first_seen=2024-05-20 | swagger: last_seen=2026-06-01, first_seen=2025-08-17 | html: last_seen=2026-06-01, first_seen=2024-04-04 | gitlab: last_seen=2026-06-01, first_seen=2025-08-17 | vmware: last_seen=2026-06-01, first_seen=2024-04-04 | sql: last_seen=2026-06-01, first_seen=2025-08-17 | brocade: last_seen=2026-06-01, first_seen=2024-05-20 | selenium webdriver: last_seen=2026-06-01, first_seen=2026-01-18 | nvidia: last_seen=2026-06-01, first_seen=2024-04-29 | f5: last_seen=2026-06-01, first_seen=2025-08-17 | bitsight: last_seen=2026-06-01, first_seen=2026-01-25 | vmware vsphere: last_seen=2026-06-01, first_seen=2025-02-20 | lucidchart: last_seen=2026-06-01, first_seen=2025-08-17 | apache flink: last_seen=2026-06-01, first_seen=2025-02-18 | quartz scheduler: last_seen=2026-06-01, first_seen=2026-03-29 | heatmap: last_seen=2026-06-01, first_seen=2025-08-17 | selenium: last_seen=2026-06-01, first_seen=2024-04-04 | owasp: last_seen=2026-06-01, first_seen=2025-08-17 | google ads: last_seen=2026-06-01, first_seen=2024-05-20 | seg: last_seen=2026-06-01, first_seen=2026-06-01 | automated insights: last_seen=2026-06-01, first_seen=2026-03-09 | asp: last_seen=2026-06-01, first_seen=2025-08-17 | microsoft office 365: last_seen=2026-06-01, first_seen=2025-02-18 | tiktok: last_seen=2026-06-01, first_seen=2024-04-22 | sungard: last_seen=2026-06-01, first_seen=2025-12-01 | microsoft visio: last_seen=2026-06-01, first_seen=2026-01-25 | rds: last_seen=2026-06-01, first_seen=2024-04-04 | camunda: last_seen=2026-06-01, first_seen=2025-03-24 | vmware horizon: last_seen=2026-06-01, first_seen=2025-08-31 | togaf: last_seen=2026-06-01, first_seen=2025-08-17 | microsoft azure: last_seen=2026-06-01, first_seen=2025-02-18 | cisco meraki: last_seen=2026-06-01, first_seen=2025-04-08 | apple watch: last_seen=2026-06-01, first_seen=2025-08-17 | teradata: last_seen=2026-06-01, first_seen=2024-05-20 | nominum: last_seen=2026-06-01, first_seen=2025-08-17 | tenable: last_seen=2026-06-01, first_seen=2025-08-17 | microsoft word: last_seen=2026-06-01, first_seen=2025-02-18 | user interviews: last_seen=2026-06-01, first_seen=2024-05-20 | vidyo: last_seen=2026-06-01, first_seen=2025-08-17 | sailpoint: last_seen=2026-06-01, first_seen=2025-08-17 | helpdesk: last_seen=2026-06-01, first_seen=2025-08-17 | adobe experience manager: last_seen=2026-06-01, first_seen=2025-02-18 | tableau: last_seen=2026-06-01, first_seen=2025-08-17 | emc vnx: last_seen=2026-06-01, first_seen=2025-08-17 | akamai: last_seen=2026-06-01, first_seen=2025-08-17 | smokeping: last_seen=2026-06-01, first_seen=2025-11-24 | jquery: last_seen=2026-06-01, first_seen=2024-04-04 | css3: last_seen=2026-06-01, first_seen=2025-08-17 | testng: last_seen=2026-06-01, first_seen=2026-01-18 | scala: last_seen=2026-06-01, first_seen=2025-08-17 | threatconnect: last_seen=2026-06-01, first_seen=2025-10-27 | trend micro: last_seen=2026-05-18, first_seen=2025-11-24 | apache jmeter: last_seen=2026-05-18, first_seen=2025-08-17 | cisco catalyst: last_seen=2026-05-18, first_seen=2025-08-17 | onramp: last_seen=2026-05-18, first_seen=2025-10-19 | ignite digital: last_seen=2026-05-18, first_seen=2025-08-17 | ekahau: last_seen=2026-05-04, first_seen=2024-05-20 | media asset management: last_seen=2026-05-04, first_seen=2025-08-17 | autocad: last_seen=2026-05-04, first_seen=2024-04-04 | eastnets: last_seen=2026-05-04, first_seen=2024-05-20 | archicad: last_seen=2026-05-04, first_seen=2025-11-11 | sketchup: last_seen=2026-05-04, first_seen=2025-11-11 | alm: last_seen=2026-04-27, first_seen=2025-08-17 | odata: last_seen=2026-04-20, first_seen=2025-08-17 | icertis: last_seen=2026-04-20, first_seen=2025-08-17 | datarobot: last_seen=2026-04-20, first_seen=2025-08-17 | mcafee: last_seen=2026-04-20, first_seen=2024-05-20 | splunk enterprise: last_seen=2026-04-20, first_seen=2026-01-25 | amazon connect: last_seen=2026-04-13, first_seen=2025-10-20 | genesys: last_seen=2026-04-13, first_seen=2025-10-20 | cisco webex: last_seen=2026-04-13, first_seen=2025-10-20 | asic: last_seen=2026-04-13, first_seen=2025-10-20 | mariadb: last_seen=2026-04-13, first_seen=2024-04-04 | snort: last_seen=2026-04-13, first_seen=2025-10-20 | yara: last_seen=2026-04-13, first_seen=2025-10-20 | apache storm: last_seen=2026-04-13, first_seen=2025-10-20 | infosys: last_seen=2026-04-13, first_seen=2025-10-20 | jamf: last_seen=2026-04-06, first_seen=2025-08-31 | microsoft windows server: last_seen=2026-04-06, first_seen=2026-01-26 | mixpanel: last_seen=2026-04-06, first_seen=2025-10-07 | sap training: last_seen=2026-04-06, first_seen=2025-10-13 | crowdstrike: last_seen=2026-04-06, first_seen=2025-03-31 | mobileiron: last_seen=2026-04-06, first_seen=2024-07-15 | google bigquery: last_seen=2026-03-30, first_seen=2025-08-24 | flutter: last_seen=2026-03-30, first_seen=2026-03-30 | jupyter: last_seen=2026-03-23, first_seen=2025-09-15 | presidio: last_seen=2026-03-23, first_seen=2025-09-21 | pytest: last_seen=2026-03-23, first_seen=2026-01-26 | hibernate: last_seen=2026-03-10, first_seen=2024-04-04 | oracle weblogic: last_seen=2026-03-10, first_seen=2025-08-17 | core hr: last_seen=2026-02-23, first_seen=2025-08-31 | centric digital: last_seen=2026-02-23, first_seen=2025-08-17 | nis: last_seen=2026-02-16, first_seen=2026-02-09 | core dna: last_seen=2026-02-16, first_seen=2025-08-24 | bpmn: last_seen=2026-02-16, first_seen=2025-08-17 | dell boomi: last_seen=2026-02-16, first_seen=2025-08-24 | macos: last_seen=2026-02-09, first_seen=2025-08-17 | microsoft windows os: last_seen=2026-02-09, first_seen=2025-08-05 | sqlalchemy: last_seen=2026-02-02, first_seen=2025-08-17 | microsoft powerpoint: last_seen=2026-01-26, first_seen=2025-02-18 | oran: last_seen=2026-01-19, first_seen=2025-08-17 | mrtg: last_seen=2026-01-19, first_seen=2025-08-17 | sap security: last_seen=2026-01-19, first_seen=2025-08-17 | citrix provisioning services: last_seen=2026-01-19, first_seen=2025-08-17 | cloud campaign: last_seen=2026-01-19, first_seen=2025-08-17 | apple iphone: last_seen=2026-01-19, first_seen=2025-08-17 | citrix xendesktop: last_seen=2026-01-19, first_seen=2025-08-17 | hugging face: last_seen=2026-01-19, first_seen=2025-08-05 | citrix netscaler: last_seen=2026-01-19, first_seen=2025-08-05 | vmware vcloud director: last_seen=2026-01-19, first_seen=2025-10-13 | storsimple: last_seen=2026-01-19, first_seen=2025-10-13 | juniper switches: last_seen=2026-01-19, first_seen=2025-08-17 | aws backup: last_seen=2026-01-19, first_seen=2025-10-13 | sap process orchestration: last_seen=2026-01-12, first_seen=2025-08-17 | tradeshift: last_seen=2026-01-12, first_seen=2025-08-17 | zycus: last_seen=2026-01-12, first_seen=2025-08-17 | dnn: last_seen=2026-01-12, first_seen=2025-08-17 | oracle soa suite: last_seen=2026-01-12, first_seen=2025-08-17 | cisco ios: last_seen=2026-01-12, first_seen=2025-08-17 | oracle soa: last_seen=2026-01-12, first_seen=2025-03-24 | aws cloudformation: last_seen=2026-01-12, first_seen=2024-04-04 | adtech: last_seen=2026-01-12, first_seen=2025-08-17 | firebase: last_seen=2026-01-05, first_seen=2025-10-26 | jetpack: last_seen=2026-01-05, first_seen=2025-10-26 | android studio: last_seen=2026-01-05, first_seen=2025-10-26 | kotlin: last_seen=2026-01-05, first_seen=2025-08-17 | scrum development: last_seen=2026-01-05, first_seen=2025-10-26 | blue prism: last_seen=2025-12-29, first_seen=2025-08-17 | cortex xsoar: last_seen=2025-12-29, first_seen=2025-08-17 | istio: last_seen=2025-12-29, first_seen=2025-08-17 | linkedin recruiter: last_seen=2025-12-22, first_seen=2025-08-05 | openlayers: last_seen=2025-12-22, first_seen=2025-08-17 | clickhouse: last_seen=2025-12-22, first_seen=2025-08-17 | spring framework: last_seen=2025-12-22, first_seen=2025-02-18 | improve digital: last_seen=2025-12-15, first_seen=2025-08-17 | alteryx: last_seen=2025-12-15, first_seen=2025-08-05 | amazon redshift: last_seen=2025-12-15, first_seen=2025-08-05 | trifacta: last_seen=2025-12-15, first_seen=2025-08-05 | persona: last_seen=2025-12-15, first_seen=2025-08-17 | couchbase: last_seen=2025-12-15, first_seen=2025-08-17 | trello: last_seen=2025-12-08, first_seen=2024-09-09 | microsoft entra: last_seen=2025-12-08, first_seen=2025-08-17 | elog: last_seen=2025-12-08, first_seen=2025-08-17 | hubspot: last_seen=2025-11-19, first_seen=2025-08-17 | rfpio: last_seen=2025-11-11, first_seen=2025-08-17 | alibaba cloud: last_seen=2025-11-11, first_seen=2025-08-05 | apache ant: last_seen=2025-10-20, first_seen=2025-07-07 | ibwave design: last_seen=2025-10-20, first_seen=2025-09-29 | kontera: last_seen=2025-10-20, first_seen=2025-10-05 | salesforce soql: last_seen=2025-10-20, first_seen=2025-08-17 | citynet: last_seen=2025-10-20, first_seen=2025-10-05 | adconion: last_seen=2025-10-20, first_seen=2025-10-05 | dmarc: last_seen=2025-10-20, first_seen=2025-08-17 | salesforce cpq: last_seen=2025-10-20, first_seen=2025-08-05 | autorabit: last_seen=2025-10-20, first_seen=2025-08-17 | ibwave: last_seen=2025-10-20, first_seen=2025-09-29 | oracle 12c: last_seen=2025-10-13, first_seen=2025-10-12 | sybase database: last_seen=2025-10-13, first_seen=2025-10-12 | sql advantage: last_seen=2025-10-07, first_seen=2025-08-17 | software ag: last_seen=2025-10-07, first_seen=2025-08-17 | webmethods: last_seen=2025-10-07, first_seen=2025-08-05 | carbon black: last_seen=2025-09-22, first_seen=2025-08-17 | docusign: last_seen=2025-09-22, first_seen=2025-03-24 | sap concur: last_seen=2025-09-15, first_seen=2025-01-28 | hootsuite: last_seen=2025-09-08, first_seen=2024-05-20 | sqs: last_seen=2025-09-08, first_seen=2024-04-04 | dds: last_seen=2025-09-08, first_seen=2025-08-17 | hcm: last_seen=2025-09-08, first_seen=2025-04-08 | blue coat: last_seen=2025-09-08, first_seen=2025-08-17 | sysomos: last_seen=2025-09-08, first_seen=2025-08-17 | sprinklr: last_seen=2025-09-08, first_seen=2025-08-17 | huddle: last_seen=2025-09-08, first_seen=2025-08-17 | cisco sourcefire: last_seen=2025-09-08, first_seen=2025-08-17 | ccn: last_seen=2025-09-08, first_seen=2025-08-17 | unify: last_seen=2025-08-25, first_seen=2025-08-17 | whatsup gold: last_seen=2025-08-25, first_seen=2025-08-17 | msi: last_seen=2025-08-17, first_seen=2025-08-17 | recharge: last_seen=2025-08-11, first_seen=2024-05-20 | mix: last_seen=2025-08-11, first_seen=2024-04-04 | medium: last_seen=2025-08-11, first_seen=2024-04-04 | segment: last_seen=2025-08-11, first_seen=2024-04-04 | zoom: last_seen=2025-08-11, first_seen=2024-04-04 | cucumber: last_seen=2025-08-11, first_seen=2024-04-04 | eclipse: last_seen=2025-08-11, first_seen=2024-04-04 | ecc: last_seen=2025-08-11, first_seen=2024-04-04 | drift: last_seen=2025-08-11, first_seen=2024-08-05 | square: last_seen=2025-08-11, first_seen=2024-05-20 | quickbooks: last_seen=2025-08-11, first_seen=2025-08-05 | unity: last_seen=2025-08-11, first_seen=2024-04-04 | ups: last_seen=2025-08-11, first_seen=2024-04-04 | charter: last_seen=2025-08-11, first_seen=2024-04-04 | visa: last_seen=2025-08-11, first_seen=2024-04-04 | spring: last_seen=2025-08-11, first_seen=2024-04-04 | amp: last_seen=2025-08-11, first_seen=2024-05-20 | juniper: last_seen=2025-08-11, first_seen=2024-04-04 | stats: last_seen=2025-08-11, first_seen=2024-04-04 | box: last_seen=2025-08-11, first_seen=2024-04-04 | c: last_seen=2025-08-11, first_seen=2024-04-04 | ease: last_seen=2025-08-11, first_seen=2024-04-04 | instagram: last_seen=2025-08-11, first_seen=2024-05-20</t>
+          <t>mysql: last_seen=2026-06-01, first_seen=2024-04-04 | nosql: last_seen=2026-06-01, first_seen=2024-07-01 | jira: last_seen=2026-06-01, first_seen=2025-08-17 | bash: last_seen=2026-06-01, first_seen=2025-08-17 | ubuntu: last_seen=2026-06-01, first_seen=2024-04-04 | oauth: last_seen=2026-06-01, first_seen=2026-05-18 | chrome: last_seen=2026-06-01, first_seen=2024-05-20 | microservices: last_seen=2026-06-01, first_seen=2025-08-24 | redis: last_seen=2026-06-01, first_seen=2024-04-04 | selenium: last_seen=2026-06-01, first_seen=2024-04-04 | microsoft excel: last_seen=2026-06-01, first_seen=2025-02-18 | figma: last_seen=2026-06-01, first_seen=2024-04-04 | nvme: last_seen=2026-06-01, first_seen=2025-08-17 | influential: last_seen=2026-06-01, first_seen=2024-04-04 | react: last_seen=2026-06-01, first_seen=2024-04-04 | google sheets: last_seen=2026-06-01, first_seen=2024-05-06 | tableau: last_seen=2026-06-01, first_seen=2025-08-17 | zoom rooms: last_seen=2026-06-01, first_seen=2026-05-18 | macos: last_seen=2026-06-01, first_seen=2025-08-17 | webpack: last_seen=2026-06-01, first_seen=2024-05-20 | appsheet: last_seen=2026-06-01, first_seen=2025-12-01 | grafana: last_seen=2026-06-01, first_seen=2024-04-04 | appsflyer: last_seen=2026-06-01, first_seen=2026-01-11 | centos: last_seen=2026-06-01, first_seen=2024-04-04 | nms: last_seen=2026-06-01, first_seen=2025-08-17 | scala: last_seen=2026-06-01, first_seen=2025-08-17 | confluence: last_seen=2026-06-01, first_seen=2025-08-17 | alteryx: last_seen=2026-06-01, first_seen=2024-11-25 | sql: last_seen=2026-06-01, first_seen=2025-08-17 | css: last_seen=2026-06-01, first_seen=2025-08-17 | protobuf: last_seen=2026-06-01, first_seen=2025-08-17 | bareos: last_seen=2026-06-01, first_seen=2026-04-28 | palo alto firewalls: last_seen=2026-06-01, first_seen=2025-08-17 | presto: last_seen=2026-06-01, first_seen=2025-08-17 | dell san: last_seen=2026-06-01, first_seen=2025-08-17 | boolean: last_seen=2026-06-01, first_seen=2025-08-17 | linux: last_seen=2026-06-01, first_seen=2024-04-04 | facebook ads: last_seen=2026-06-01, first_seen=2026-01-25 | git: last_seen=2026-06-01, first_seen=2024-04-04 | css3: last_seen=2026-06-01, first_seen=2025-08-17 | inmobi: last_seen=2026-06-01, first_seen=2025-08-17 | iam: last_seen=2026-06-01, first_seen=2025-01-06 | junit: last_seen=2026-06-01, first_seen=2025-08-24 | angular: last_seen=2026-06-01, first_seen=2024-04-04 | google workspace: last_seen=2026-06-01, first_seen=2024-05-20 | kubernetes: last_seen=2026-06-01, first_seen=2024-04-04 | fortinet: last_seen=2026-06-01, first_seen=2024-11-04 | helm: last_seen=2026-06-01, first_seen=2026-01-25 | microsoft 365: last_seen=2026-06-01, first_seen=2025-08-17 | youtube: last_seen=2026-06-01, first_seen=2024-05-20 | hive: last_seen=2026-06-01, first_seen=2026-01-25 | tiktok: last_seen=2026-06-01, first_seen=2025-04-08 | clickup: last_seen=2026-06-01, first_seen=2025-01-13 | redux: last_seen=2026-06-01, first_seen=2024-05-20 | pci: last_seen=2026-06-01, first_seen=2025-08-17 | nginx: last_seen=2026-06-01, first_seen=2024-04-04 | selenium webdriver: last_seen=2026-06-01, first_seen=2026-04-27 | vmware: last_seen=2026-06-01, first_seen=2024-04-04 | flask: last_seen=2026-06-01, first_seen=2025-08-17 | logstash: last_seen=2026-06-01, first_seen=2024-05-20 | jira service desk: last_seen=2026-06-01, first_seen=2025-08-05 | cisco anyconnect: last_seen=2026-06-01, first_seen=2024-07-01 | cisco firewalls: last_seen=2026-06-01, first_seen=2025-08-17 | splunk: last_seen=2026-06-01, first_seen=2024-05-20 | nvidia: last_seen=2026-06-01, first_seen=2025-03-10 | freshservice: last_seen=2026-06-01, first_seen=2025-08-17 | google cloud: last_seen=2026-06-01, first_seen=2024-04-22 | freshdesk: last_seen=2026-06-01, first_seen=2026-05-25 | cisco nexus: last_seen=2026-06-01, first_seen=2025-08-17 | mongodb: last_seen=2026-06-01, first_seen=2025-04-08 | cisco switches: last_seen=2026-06-01, first_seen=2024-07-01 | cuda: last_seen=2026-06-01, first_seen=2025-08-17 | eslint: last_seen=2026-06-01, first_seen=2025-08-17 | python: last_seen=2026-06-01, first_seen=2024-04-04 | blockchain: last_seen=2026-06-01, first_seen=2025-08-17 | linux shell: last_seen=2026-06-01, first_seen=2026-02-09 | freepbx: last_seen=2026-06-01, first_seen=2025-08-17 | fintech: last_seen=2026-06-01, first_seen=2025-08-17 | hackerone: last_seen=2026-06-01, first_seen=2025-08-17 | debian: last_seen=2026-06-01, first_seen=2024-07-01 | google drive: last_seen=2026-06-01, first_seen=2026-05-18 | cisco asa: last_seen=2026-06-01, first_seen=2024-05-20 | jenkins: last_seen=2026-06-01, first_seen=2024-04-04 | react native: last_seen=2026-06-01, first_seen=2025-02-18 | helpdesk: last_seen=2026-06-01, first_seen=2025-08-17 | graphql: last_seen=2026-06-01, first_seen=2025-08-05 | servicenow: last_seen=2026-06-01, first_seen=2024-04-04 | livestream: last_seen=2026-06-01, first_seen=2025-08-17 | elastic: last_seen=2026-06-01, first_seen=2025-08-17 | testrail: last_seen=2026-06-01, first_seen=2026-04-06 | verizon: last_seen=2026-06-01, first_seen=2024-05-20 | qlik: last_seen=2026-06-01, first_seen=2025-12-15 | saltstack: last_seen=2026-06-01, first_seen=2024-04-04 | f5: last_seen=2026-06-01, first_seen=2025-08-17 | typescript: last_seen=2026-06-01, first_seen=2025-08-17 | elk: last_seen=2026-06-01, first_seen=2024-12-09 | power bi: last_seen=2026-06-01, first_seen=2025-08-17 | django: last_seen=2026-06-01, first_seen=2024-04-04 | docker: last_seen=2026-06-01, first_seen=2024-04-04 | broadcom: last_seen=2026-06-01, first_seen=2025-08-17 | windows server: last_seen=2026-06-01, first_seen=2025-08-17 | idc: last_seen=2026-06-01, first_seen=2025-08-17 | twitter: last_seen=2026-06-01, first_seen=2025-04-08 | cisco routers: last_seen=2026-06-01, first_seen=2024-07-01 | google ads: last_seen=2026-06-01, first_seen=2026-01-25 | ansible: last_seen=2026-06-01, first_seen=2024-04-04 | facebook: last_seen=2026-06-01, first_seen=2024-04-29 | rpa: last_seen=2026-06-01, first_seen=2025-08-17 | testng: last_seen=2026-06-01, first_seen=2026-04-27 | openvpn: last_seen=2026-06-01, first_seen=2024-07-01 | seagate: last_seen=2026-06-01, first_seen=2025-08-17 | playwright: last_seen=2026-06-01, first_seen=2025-11-03 | huawei switches: last_seen=2026-06-01, first_seen=2025-08-17 | charles proxy: last_seen=2026-06-01, first_seen=2026-01-25 | html5: last_seen=2026-06-01, first_seen=2025-08-17 | pytorch: last_seen=2026-06-01, first_seen=2025-08-17 | php: last_seen=2026-06-01, first_seen=2024-05-13 | microsoft: last_seen=2026-06-01, first_seen=2024-04-04 | pytest: last_seen=2026-06-01, first_seen=2026-01-04 | centric digital: last_seen=2026-06-01, first_seen=2025-08-17 | group policy: last_seen=2026-06-01, first_seen=2025-08-17 | huawei: last_seen=2026-06-01, first_seen=2025-08-17 | microsoft power bi: last_seen=2026-06-01, first_seen=2025-04-08 | dell: last_seen=2026-06-01, first_seen=2024-05-20 | javafx: last_seen=2026-06-01, first_seen=2025-08-17 | gitlab: last_seen=2026-06-01, first_seen=2025-08-17 | sd wan: last_seen=2026-06-01, first_seen=2025-08-17 | crowdstrike: last_seen=2026-06-01, first_seen=2026-05-04 | html: last_seen=2026-06-01, first_seen=2024-04-04 | jupyter: last_seen=2026-06-01, first_seen=2026-04-28 | trello: last_seen=2026-06-01, first_seen=2024-04-04 | qlik sense: last_seen=2026-06-01, first_seen=2025-12-15 | oracle 11g: last_seen=2026-06-01, first_seen=2025-08-17 | appium: last_seen=2026-06-01, first_seen=2024-04-04 | jest: last_seen=2026-06-01, first_seen=2025-08-17 | google calendar: last_seen=2026-06-01, first_seen=2024-05-20 | oracle: last_seen=2026-06-01, first_seen=2025-08-17 | elasticsearch: last_seen=2026-06-01, first_seen=2025-03-03 | sipp: last_seen=2026-06-01, first_seen=2025-08-17 | java: last_seen=2026-06-01, first_seen=2024-04-04 | kibana: last_seen=2026-06-01, first_seen=2025-08-17 | hcm: last_seen=2026-06-01, first_seen=2024-04-22 | twitch: last_seen=2026-06-01, first_seen=2025-08-17 | centurylink: last_seen=2026-06-01, first_seen=2025-08-17 | prometheus: last_seen=2026-06-01, first_seen=2024-04-04 | grpc: last_seen=2026-06-01, first_seen=2025-08-17 | user interviews: last_seen=2026-06-01, first_seen=2024-04-04 | gmail: last_seen=2026-06-01, first_seen=2024-05-20 | postman: last_seen=2026-06-01, first_seen=2024-07-01 | greenhouse: last_seen=2026-06-01, first_seen=2024-05-20 | github actions: last_seen=2026-06-01, first_seen=2026-04-27 | zabbix: last_seen=2026-06-01, first_seen=2024-04-04 | javascript: last_seen=2026-06-01, first_seen=2024-04-04 | samsung: last_seen=2026-06-01, first_seen=2025-08-17 | github: last_seen=2026-06-01, first_seen=2026-04-27 | materialize: last_seen=2026-06-01, first_seen=2024-04-22 | microsoft office: last_seen=2026-05-25, first_seen=2025-12-01 | hugging face: last_seen=2026-05-18, first_seen=2025-11-24 | openai: last_seen=2026-05-18, first_seen=2025-11-24 | liveops: last_seen=2026-05-11, first_seen=2026-04-19 | prototype: last_seen=2026-05-04, first_seen=2024-08-20 | kotlin: last_seen=2026-05-04, first_seen=2025-11-11 | arista switches: last_seen=2026-04-27, first_seen=2025-11-03 | windows 10: last_seen=2026-04-20, first_seen=2025-10-26 | whatsapp: last_seen=2026-04-20, first_seen=2025-08-17 | workspace one: last_seen=2026-04-20, first_seen=2025-08-17 | q4: last_seen=2026-04-13, first_seen=2025-08-31 | tensorflow: last_seen=2026-04-06, first_seen=2025-08-17 | latex: last_seen=2026-03-10, first_seen=2025-08-17 | hbase: last_seen=2026-02-23, first_seen=2024-04-04 | json: last_seen=2026-02-23, first_seen=2024-04-04 | katalon: last_seen=2026-02-16, first_seen=2026-01-04 | soapui: last_seen=2026-02-16, first_seen=2025-08-24 | dql: last_seen=2026-02-16, first_seen=2026-01-04 | postgresql: last_seen=2026-02-16, first_seen=2024-04-04 | unix: last_seen=2026-02-02, first_seen=2024-04-04 | honeywell: last_seen=2026-01-26, first_seen=2026-01-12 | honeywell ebi: last_seen=2026-01-26, first_seen=2026-01-12 | johnson controls metasys: last_seen=2026-01-26, first_seen=2026-01-12 | autocad: last_seen=2026-01-26, first_seen=2026-01-12 | kyriba: last_seen=2026-01-05, first_seen=2024-11-18 | wireshark: last_seen=2025-12-22, first_seen=2025-08-05 | ssh: last_seen=2025-12-22, first_seen=2025-08-17 | tcpdump: last_seen=2025-12-22, first_seen=2025-08-17 | red hat: last_seen=2025-12-22, first_seen=2025-08-05 | linux kernel: last_seen=2025-12-22, first_seen=2025-08-17 | salesforce: last_seen=2025-12-15, first_seen=2025-07-28 | beyondtrust: last_seen=2025-12-08, first_seen=2025-08-17 | jamf: last_seen=2025-12-08, first_seen=2025-08-17 | cacti: last_seen=2025-12-08, first_seen=2025-08-17 | flutter: last_seen=2025-11-19, first_seen=2024-12-23 | veeam: last_seen=2025-11-03, first_seen=2025-06-12 | looker: last_seen=2025-10-13, first_seen=2024-07-29 | purecloud: last_seen=2025-10-13, first_seen=2025-08-17 | google docs: last_seen=2025-10-13, first_seen=2025-03-24 | openstack: last_seen=2025-10-13, first_seen=2024-04-22 | rsa: last_seen=2025-09-08, first_seen=2025-08-17 | rsa archer: last_seen=2025-09-08, first_seen=2025-04-08 | vmware esxi: last_seen=2025-09-08, first_seen=2025-04-08 | microsoft windows server: last_seen=2025-09-08, first_seen=2025-04-08 | netsuite: last_seen=2025-09-08, first_seen=2025-03-17 | acer: last_seen=2025-09-08, first_seen=2025-08-17 | stats: last_seen=2025-08-11, first_seen=2024-05-20 | ease: last_seen=2025-08-11, first_seen=2024-04-04 | ups: last_seen=2025-08-11, first_seen=2024-04-04 | amp: last_seen=2025-08-11, first_seen=2024-05-20 | upkeep: last_seen=2025-08-11, first_seen=2025-04-07 | box: last_seen=2025-08-11, first_seen=2024-04-04 | tailwind: last_seen=2025-08-11, first_seen=2025-08-05 | juniper: last_seen=2025-08-11, first_seen=2024-05-20 | medium: last_seen=2025-08-11, first_seen=2024-04-04 | segment: last_seen=2025-08-11, first_seen=2024-04-04 | c: last_seen=2025-08-11, first_seen=2024-04-04 | slack: last_seen=2025-08-11, first_seen=2024-07-01 | market leader: last_seen=2025-08-11, first_seen=2024-05-20 | charter: last_seen=2025-08-11, first_seen=2024-04-22 | zoom: last_seen=2025-08-11, first_seen=2024-05-20 | impact: last_seen=2025-08-11, first_seen=2024-04-04 | instagram: last_seen=2025-08-11, first_seen=2025-04-08 | storybook: last_seen=2025-08-11, first_seen=2025-08-05 | network solutions: last_seen=2025-08-11, first_seen=2025-04-08 | well: last_seen=2025-07-28, first_seen=2024-04-04 | swift: last_seen=2025-06-12, first_seen=2024-05-20 | apache hadoop: last_seen=2025-06-12, first_seen=2025-02-20 | vmware vcenter: last_seen=2025-06-12, first_seen=2025-06-12 | apache: last_seen=2025-06-12, first_seen=2024-05-20 | intercom: last_seen=2025-06-12, first_seen=2025-04-08 | ey: last_seen=2025-06-12, first_seen=2024-07-29 | oracle ebs: last_seen=2025-06-09, first_seen=2024-05-13 | haproxy: last_seen=2025-06-09, first_seen=2024-04-04 | asana: last_seen=2025-06-09, first_seen=2025-01-13 | openresty: last_seen=2025-06-09, first_seen=2024-04-04 | nunit: last_seen=2025-03-31, first_seen=2024-05-20 | vmware vsphere: last_seen=2025-03-24, first_seen=2025-02-18 | terraform: last_seen=2025-03-24, first_seen=2024-04-04 | nodejs: last_seen=2025-03-10, first_seen=2024-04-04 | vue.js: last_seen=2025-02-10, first_seen=2024-12-23 | ruby on rails: last_seen=2025-02-10, first_seen=2024-06-24 | rabbitmq: last_seen=2025-01-20, first_seen=2024-07-29 | cucumber: last_seen=2024-12-23, first_seen=2024-07-01 | sprint: last_seen=2024-11-13, first_seen=2024-06-10 | adobe: last_seen=2024-09-02, first_seen=2024-04-04 | miro: last_seen=2024-08-26, first_seen=2024-05-20 | transcend: last_seen=2024-08-26, first_seen=2024-07-29 | visa: last_seen=2024-08-12, first_seen=2024-04-04 | nagios: last_seen=2024-06-03, first_seen=2024-05-20 | freshworks: last_seen=2024-05-27, first_seen=2024-04-04 | zapier: last_seen=2024-05-06, first_seen=2024-04-04</t>
         </is>
       </c>
     </row>
